--- a/projects/auto_page/autopageMKII/tables/Accel_mode_test.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode_test.xlsx
@@ -13,10 +13,10 @@
     <sheet name="Processed_Logs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$C$306</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$D$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed_Orders'!$A$1:$C$150</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Processed_Logs'!$A$1:$I$208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$C$289</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed_Orders'!$A$1:$C$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Processed_Logs'!$A$1:$I$212</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -319,7 +319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C306"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="4" min="1" max="1"/>
@@ -351,11 +351,7 @@
           <t>SU564M5AA</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>SU564M5AA</t>
-        </is>
-      </c>
+      <c r="C2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr"/>
@@ -364,11 +360,7 @@
           <t>SU564M5PC</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>SU564M5PC</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr"/>
@@ -377,11 +369,7 @@
           <t>SU564M9WN</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>SU564M9WN</t>
-        </is>
-      </c>
+      <c r="C4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr"/>
@@ -390,11 +378,7 @@
           <t>SU564M9B0</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>SU564M9B0</t>
-        </is>
-      </c>
+      <c r="C5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr"/>
@@ -403,11 +387,7 @@
           <t>SU564MB82</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>SU564MB82</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr"/>
@@ -416,11 +396,7 @@
           <t>SU564MANM</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>SU564MANM</t>
-        </is>
-      </c>
+      <c r="C7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr"/>
@@ -429,11 +405,7 @@
           <t>SU564M928</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>SU564M928</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr"/>
@@ -1540,11 +1512,7 @@
       <c r="C208" s="3" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="inlineStr">
-        <is>
-          <t>2610205CASVS3V</t>
-        </is>
-      </c>
+      <c r="A209" s="3" t="inlineStr"/>
       <c r="B209" s="3" t="inlineStr"/>
       <c r="C209" s="3" t="inlineStr"/>
     </row>
@@ -1584,159 +1552,119 @@
       <c r="C216" s="3" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="inlineStr">
-        <is>
-          <t>2610205CBKM7J1</t>
-        </is>
-      </c>
+      <c r="A217" s="3" t="inlineStr"/>
       <c r="B217" s="3" t="inlineStr"/>
       <c r="C217" s="3" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>2610205CDYVPEK</t>
-        </is>
-      </c>
+      <c r="A218" s="3" t="inlineStr"/>
       <c r="B218" s="3" t="inlineStr"/>
       <c r="C218" s="3" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="inlineStr">
-        <is>
-          <t>2610205CT8S089</t>
-        </is>
-      </c>
+      <c r="A219" s="3" t="inlineStr"/>
       <c r="B219" s="3" t="inlineStr"/>
       <c r="C219" s="3" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="inlineStr">
-        <is>
-          <t>2610205D58Q0TW</t>
-        </is>
-      </c>
+      <c r="A220" s="3" t="inlineStr"/>
       <c r="B220" s="3" t="inlineStr"/>
       <c r="C220" s="3" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="inlineStr">
-        <is>
-          <t>2610205DHCUBGF</t>
-        </is>
-      </c>
+      <c r="A221" s="3" t="inlineStr"/>
       <c r="B221" s="3" t="inlineStr"/>
       <c r="C221" s="3" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>2610205FNF148X</t>
-        </is>
-      </c>
+      <c r="A222" s="3" t="inlineStr"/>
       <c r="B222" s="3" t="inlineStr"/>
       <c r="C222" s="3" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="inlineStr">
-        <is>
-          <t>2610205FQKPQXJ</t>
-        </is>
-      </c>
+      <c r="A223" s="3" t="inlineStr"/>
       <c r="B223" s="3" t="inlineStr"/>
       <c r="C223" s="3" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="inlineStr">
-        <is>
-          <t>2610205G2A487N</t>
-        </is>
-      </c>
+      <c r="A224" s="3" t="inlineStr"/>
       <c r="B224" s="3" t="inlineStr"/>
       <c r="C224" s="3" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="inlineStr">
-        <is>
-          <t>2610205G9TDVEK</t>
-        </is>
-      </c>
+      <c r="A225" s="3" t="inlineStr"/>
       <c r="B225" s="3" t="inlineStr"/>
       <c r="C225" s="3" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="inlineStr">
-        <is>
-          <t>2610205GG0RJP3</t>
-        </is>
-      </c>
+      <c r="A226" s="3" t="inlineStr"/>
       <c r="B226" s="3" t="inlineStr"/>
       <c r="C226" s="3" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="inlineStr">
-        <is>
-          <t>2610205GTHDX0T</t>
-        </is>
-      </c>
+      <c r="A227" s="3" t="inlineStr"/>
       <c r="B227" s="3" t="inlineStr"/>
       <c r="C227" s="3" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="inlineStr">
-        <is>
-          <t>2610205JC2CXHC</t>
-        </is>
-      </c>
+      <c r="A228" s="3" t="inlineStr"/>
       <c r="B228" s="3" t="inlineStr"/>
       <c r="C228" s="3" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="3" t="inlineStr">
         <is>
-          <t>2610205K0V2QCE</t>
+          <t>2610218A2WCX78</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr"/>
       <c r="C229" s="3" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="inlineStr">
-        <is>
-          <t>2610205K1KX372</t>
-        </is>
-      </c>
+      <c r="A230" s="3" t="inlineStr"/>
       <c r="B230" s="3" t="inlineStr"/>
       <c r="C230" s="3" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="3" t="inlineStr">
         <is>
-          <t>2610205KU39SPS</t>
+          <t>2610218AQHBP4W</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr"/>
       <c r="C231" s="3" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="inlineStr"/>
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>2610218AVNB1FC</t>
+        </is>
+      </c>
       <c r="B232" s="3" t="inlineStr"/>
       <c r="C232" s="3" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="inlineStr"/>
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>2610218B0GCAQ7</t>
+        </is>
+      </c>
       <c r="B233" s="3" t="inlineStr"/>
       <c r="C233" s="3" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="inlineStr"/>
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>2610218B5CQQXM</t>
+        </is>
+      </c>
       <c r="B234" s="3" t="inlineStr"/>
       <c r="C234" s="3" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="3" t="inlineStr">
         <is>
-          <t>2610205KXHY6J1</t>
+          <t>2610218B7GGDFK</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr"/>
@@ -1745,7 +1673,7 @@
     <row r="236">
       <c r="A236" s="3" t="inlineStr">
         <is>
-          <t>2610205MG0TMXX</t>
+          <t>2610218BA3FF4J</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr"/>
@@ -1754,7 +1682,7 @@
     <row r="237">
       <c r="A237" s="3" t="inlineStr">
         <is>
-          <t>2610205MSWCKV5</t>
+          <t>2610218BCU6S4C</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr"/>
@@ -1763,7 +1691,7 @@
     <row r="238">
       <c r="A238" s="3" t="inlineStr">
         <is>
-          <t>2610205P8RJJAR</t>
+          <t>2610218DKJ9V5R</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr"/>
@@ -1772,7 +1700,7 @@
     <row r="239">
       <c r="A239" s="3" t="inlineStr">
         <is>
-          <t>2610205PB5T1B5</t>
+          <t>2610218E7H6T2H</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr"/>
@@ -1781,7 +1709,7 @@
     <row r="240">
       <c r="A240" s="3" t="inlineStr">
         <is>
-          <t>2610205PWM4F63</t>
+          <t>2610218ESUQDK6</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr"/>
@@ -1790,7 +1718,7 @@
     <row r="241">
       <c r="A241" s="3" t="inlineStr">
         <is>
-          <t>2610205QF228C5</t>
+          <t>2610218EYY7KAX</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr"/>
@@ -1799,7 +1727,7 @@
     <row r="242">
       <c r="A242" s="3" t="inlineStr">
         <is>
-          <t>2610205REK3DPP</t>
+          <t>2610218F8UENKE</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr"/>
@@ -1808,7 +1736,7 @@
     <row r="243">
       <c r="A243" s="3" t="inlineStr">
         <is>
-          <t>2610205RGG3S2U</t>
+          <t>2610218G11UDDF</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr"/>
@@ -1817,7 +1745,7 @@
     <row r="244">
       <c r="A244" s="3" t="inlineStr">
         <is>
-          <t>2610205RH6YHMS</t>
+          <t>2610218G4FEJWN</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr"/>
@@ -1826,7 +1754,7 @@
     <row r="245">
       <c r="A245" s="3" t="inlineStr">
         <is>
-          <t>2610205S3DPYRR</t>
+          <t>2610218G8BDVQW</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr"/>
@@ -1835,7 +1763,7 @@
     <row r="246">
       <c r="A246" s="3" t="inlineStr">
         <is>
-          <t>2610205TF1TFHF</t>
+          <t>2610218GBQ6XRH</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr"/>
@@ -1844,7 +1772,7 @@
     <row r="247">
       <c r="A247" s="3" t="inlineStr">
         <is>
-          <t>2610205TS55GMF</t>
+          <t>2610218GP5YVPD</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr"/>
@@ -1853,7 +1781,7 @@
     <row r="248">
       <c r="A248" s="3" t="inlineStr">
         <is>
-          <t>2610205U0DUH9Q</t>
+          <t>2610218GY18E99</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr"/>
@@ -1862,7 +1790,7 @@
     <row r="249">
       <c r="A249" s="3" t="inlineStr">
         <is>
-          <t>2610205U47X2N9</t>
+          <t>2610218J886G5W</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr"/>
@@ -1871,25 +1799,21 @@
     <row r="250">
       <c r="A250" s="3" t="inlineStr">
         <is>
-          <t>2610205U7TABYF</t>
+          <t>2610218JCCPEF3</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr"/>
       <c r="C250" s="3" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="inlineStr">
-        <is>
-          <t>2610205VC5TDB3</t>
-        </is>
-      </c>
+      <c r="A251" s="3" t="inlineStr"/>
       <c r="B251" s="3" t="inlineStr"/>
       <c r="C251" s="3" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="3" t="inlineStr">
         <is>
-          <t>2610205VD4AG0N</t>
+          <t>2610218MXF2W3H</t>
         </is>
       </c>
       <c r="B252" s="3" t="inlineStr"/>
@@ -1898,7 +1822,7 @@
     <row r="253">
       <c r="A253" s="3" t="inlineStr">
         <is>
-          <t>2610205VQ8JQ47</t>
+          <t>2610228RM3AEUH</t>
         </is>
       </c>
       <c r="B253" s="3" t="inlineStr"/>
@@ -1907,7 +1831,7 @@
     <row r="254">
       <c r="A254" s="3" t="inlineStr">
         <is>
-          <t>2610205VY0GVA1</t>
+          <t>2610228RQMQNX5</t>
         </is>
       </c>
       <c r="B254" s="3" t="inlineStr"/>
@@ -1916,7 +1840,7 @@
     <row r="255">
       <c r="A255" s="3" t="inlineStr">
         <is>
-          <t>2610205W9H7S74</t>
+          <t>2610228S1BMCY3</t>
         </is>
       </c>
       <c r="B255" s="3" t="inlineStr"/>
@@ -1925,7 +1849,7 @@
     <row r="256">
       <c r="A256" s="3" t="inlineStr">
         <is>
-          <t>2610205XC6AHM4</t>
+          <t>2610228S6A0634</t>
         </is>
       </c>
       <c r="B256" s="3" t="inlineStr"/>
@@ -1934,7 +1858,7 @@
     <row r="257">
       <c r="A257" s="3" t="inlineStr">
         <is>
-          <t>2610205YRQ3T98</t>
+          <t>2610228TCJF8TJ</t>
         </is>
       </c>
       <c r="B257" s="3" t="inlineStr"/>
@@ -1943,7 +1867,7 @@
     <row r="258">
       <c r="A258" s="3" t="inlineStr">
         <is>
-          <t>26102061CEQGXC</t>
+          <t>2610228TJXKXDG</t>
         </is>
       </c>
       <c r="B258" s="3" t="inlineStr"/>
@@ -1952,7 +1876,7 @@
     <row r="259">
       <c r="A259" s="3" t="inlineStr">
         <is>
-          <t>261020629NB0D3</t>
+          <t>2610228TM5QH3H</t>
         </is>
       </c>
       <c r="B259" s="3" t="inlineStr"/>
@@ -1961,7 +1885,7 @@
     <row r="260">
       <c r="A260" s="3" t="inlineStr">
         <is>
-          <t>26102062QA3DQK</t>
+          <t>2610228TPF30GW</t>
         </is>
       </c>
       <c r="B260" s="3" t="inlineStr"/>
@@ -1970,7 +1894,7 @@
     <row r="261">
       <c r="A261" s="3" t="inlineStr">
         <is>
-          <t>26102063D18SXA</t>
+          <t>2610228U3A4JWC</t>
         </is>
       </c>
       <c r="B261" s="3" t="inlineStr"/>
@@ -1979,21 +1903,25 @@
     <row r="262">
       <c r="A262" s="3" t="inlineStr">
         <is>
-          <t>26102064M0QFCW</t>
+          <t>2610228U5V70DP</t>
         </is>
       </c>
       <c r="B262" s="3" t="inlineStr"/>
       <c r="C262" s="3" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="inlineStr"/>
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>2610228UVQMWDA</t>
+        </is>
+      </c>
       <c r="B263" s="3" t="inlineStr"/>
       <c r="C263" s="3" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="3" t="inlineStr">
         <is>
-          <t>26102164T38JEK</t>
+          <t>2610228WVXTXFH</t>
         </is>
       </c>
       <c r="B264" s="3" t="inlineStr"/>
@@ -2002,7 +1930,7 @@
     <row r="265">
       <c r="A265" s="3" t="inlineStr">
         <is>
-          <t>26102167KCF00F</t>
+          <t>2610228WY6BNJ0</t>
         </is>
       </c>
       <c r="B265" s="3" t="inlineStr"/>
@@ -2011,7 +1939,7 @@
     <row r="266">
       <c r="A266" s="3" t="inlineStr">
         <is>
-          <t>26102167WX2F3M</t>
+          <t>2610228XKY1A2F</t>
         </is>
       </c>
       <c r="B266" s="3" t="inlineStr"/>
@@ -2020,7 +1948,7 @@
     <row r="267">
       <c r="A267" s="3" t="inlineStr">
         <is>
-          <t>261021698D3D7C</t>
+          <t>261022933MPUE1</t>
         </is>
       </c>
       <c r="B267" s="3" t="inlineStr"/>
@@ -2029,7 +1957,7 @@
     <row r="268">
       <c r="A268" s="3" t="inlineStr">
         <is>
-          <t>261021699RWGC3</t>
+          <t>26102298JPKH12</t>
         </is>
       </c>
       <c r="B268" s="3" t="inlineStr"/>
@@ -2038,7 +1966,7 @@
     <row r="269">
       <c r="A269" s="3" t="inlineStr">
         <is>
-          <t>2610216AQB3V23</t>
+          <t>261022991HH9F2</t>
         </is>
       </c>
       <c r="B269" s="3" t="inlineStr"/>
@@ -2047,7 +1975,7 @@
     <row r="270">
       <c r="A270" s="3" t="inlineStr">
         <is>
-          <t>2610216AXF06QF</t>
+          <t>2610229BYS1YCY</t>
         </is>
       </c>
       <c r="B270" s="3" t="inlineStr"/>
@@ -2056,7 +1984,7 @@
     <row r="271">
       <c r="A271" s="3" t="inlineStr">
         <is>
-          <t>2610216AXSJ055</t>
+          <t>2610229DK1AT9G</t>
         </is>
       </c>
       <c r="B271" s="3" t="inlineStr"/>
@@ -2065,7 +1993,7 @@
     <row r="272">
       <c r="A272" s="3" t="inlineStr">
         <is>
-          <t>2610216BF435GM</t>
+          <t>2610229DQ412YT</t>
         </is>
       </c>
       <c r="B272" s="3" t="inlineStr"/>
@@ -2074,7 +2002,7 @@
     <row r="273">
       <c r="A273" s="3" t="inlineStr">
         <is>
-          <t>2610216BV8Q9F0</t>
+          <t>2610229EGS5FMY</t>
         </is>
       </c>
       <c r="B273" s="3" t="inlineStr"/>
@@ -2083,7 +2011,7 @@
     <row r="274">
       <c r="A274" s="3" t="inlineStr">
         <is>
-          <t>2610216CUF74MR</t>
+          <t>2610229GUVC4XF</t>
         </is>
       </c>
       <c r="B274" s="3" t="inlineStr"/>
@@ -2092,7 +2020,7 @@
     <row r="275">
       <c r="A275" s="3" t="inlineStr">
         <is>
-          <t>2610216DBN2PX2</t>
+          <t>2610229J3QE34G</t>
         </is>
       </c>
       <c r="B275" s="3" t="inlineStr"/>
@@ -2101,7 +2029,7 @@
     <row r="276">
       <c r="A276" s="3" t="inlineStr">
         <is>
-          <t>2610216J6FD2VU</t>
+          <t>2610229JNGS9N4</t>
         </is>
       </c>
       <c r="B276" s="3" t="inlineStr"/>
@@ -2110,7 +2038,7 @@
     <row r="277">
       <c r="A277" s="3" t="inlineStr">
         <is>
-          <t>2610216JQRGAP6</t>
+          <t>2610229M4PDMS6</t>
         </is>
       </c>
       <c r="B277" s="3" t="inlineStr"/>
@@ -2119,7 +2047,7 @@
     <row r="278">
       <c r="A278" s="3" t="inlineStr">
         <is>
-          <t>2610216MAU45XE</t>
+          <t>2610229MG8F05S</t>
         </is>
       </c>
       <c r="B278" s="3" t="inlineStr"/>
@@ -2128,7 +2056,7 @@
     <row r="279">
       <c r="A279" s="3" t="inlineStr">
         <is>
-          <t>2610216SNPJAQA</t>
+          <t>2610229MHFJ44T</t>
         </is>
       </c>
       <c r="B279" s="3" t="inlineStr"/>
@@ -2137,7 +2065,7 @@
     <row r="280">
       <c r="A280" s="3" t="inlineStr">
         <is>
-          <t>2610216UJC80PE</t>
+          <t>2610229P3U8XPD</t>
         </is>
       </c>
       <c r="B280" s="3" t="inlineStr"/>
@@ -2146,7 +2074,7 @@
     <row r="281">
       <c r="A281" s="3" t="inlineStr">
         <is>
-          <t>2610216W9YSWT0</t>
+          <t>2610229Q0RC40D</t>
         </is>
       </c>
       <c r="B281" s="3" t="inlineStr"/>
@@ -2155,7 +2083,7 @@
     <row r="282">
       <c r="A282" s="3" t="inlineStr">
         <is>
-          <t>2610216YFS8D82</t>
+          <t>2610229Q17JXN0</t>
         </is>
       </c>
       <c r="B282" s="3" t="inlineStr"/>
@@ -2164,7 +2092,7 @@
     <row r="283">
       <c r="A283" s="3" t="inlineStr">
         <is>
-          <t>26102171E1FDBJ</t>
+          <t>2610229QQVCTYY</t>
         </is>
       </c>
       <c r="B283" s="3" t="inlineStr"/>
@@ -2173,7 +2101,7 @@
     <row r="284">
       <c r="A284" s="3" t="inlineStr">
         <is>
-          <t>26102172AJ41BU</t>
+          <t>2610229R9F3D3X</t>
         </is>
       </c>
       <c r="B284" s="3" t="inlineStr"/>
@@ -2182,7 +2110,7 @@
     <row r="285">
       <c r="A285" s="3" t="inlineStr">
         <is>
-          <t>26102173QYJSBU</t>
+          <t>2610229RQ6PKUG</t>
         </is>
       </c>
       <c r="B285" s="3" t="inlineStr"/>
@@ -2191,7 +2119,7 @@
     <row r="286">
       <c r="A286" s="3" t="inlineStr">
         <is>
-          <t>26102174G7TQWP</t>
+          <t>2610229RTMBCB4</t>
         </is>
       </c>
       <c r="B286" s="3" t="inlineStr"/>
@@ -2200,7 +2128,7 @@
     <row r="287">
       <c r="A287" s="3" t="inlineStr">
         <is>
-          <t>26102174V4CWWB</t>
+          <t>2610229SA847C1</t>
         </is>
       </c>
       <c r="B287" s="3" t="inlineStr"/>
@@ -2209,7 +2137,7 @@
     <row r="288">
       <c r="A288" s="3" t="inlineStr">
         <is>
-          <t>2610217620F70U</t>
+          <t>2610229SG5VYRN</t>
         </is>
       </c>
       <c r="B288" s="3" t="inlineStr"/>
@@ -2218,167 +2146,14 @@
     <row r="289">
       <c r="A289" s="3" t="inlineStr">
         <is>
-          <t>26102176SGXHMV</t>
+          <t>2610229SS8SW92</t>
         </is>
       </c>
       <c r="B289" s="3" t="inlineStr"/>
       <c r="C289" s="3" t="inlineStr"/>
     </row>
-    <row r="290">
-      <c r="A290" s="3" t="inlineStr">
-        <is>
-          <t>26102177UH3KJG</t>
-        </is>
-      </c>
-      <c r="B290" s="3" t="inlineStr"/>
-      <c r="C290" s="3" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t>26102178RKWC4W</t>
-        </is>
-      </c>
-      <c r="B291" s="3" t="inlineStr"/>
-      <c r="C291" s="3" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="3" t="inlineStr">
-        <is>
-          <t>26102178VHRNC6</t>
-        </is>
-      </c>
-      <c r="B292" s="3" t="inlineStr"/>
-      <c r="C292" s="3" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="3" t="inlineStr">
-        <is>
-          <t>261021790BUYXV</t>
-        </is>
-      </c>
-      <c r="B293" s="3" t="inlineStr"/>
-      <c r="C293" s="3" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="3" t="inlineStr">
-        <is>
-          <t>261021796URVP2</t>
-        </is>
-      </c>
-      <c r="B294" s="3" t="inlineStr"/>
-      <c r="C294" s="3" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="3" t="inlineStr">
-        <is>
-          <t>26102179FRWGJ1</t>
-        </is>
-      </c>
-      <c r="B295" s="3" t="inlineStr"/>
-      <c r="C295" s="3" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="3" t="inlineStr">
-        <is>
-          <t>26102179Q69ND5</t>
-        </is>
-      </c>
-      <c r="B296" s="3" t="inlineStr"/>
-      <c r="C296" s="3" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="3" t="inlineStr">
-        <is>
-          <t>2610217A4NBTHV</t>
-        </is>
-      </c>
-      <c r="B297" s="3" t="inlineStr"/>
-      <c r="C297" s="3" t="inlineStr"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="3" t="inlineStr">
-        <is>
-          <t>2610217BJ7JR54</t>
-        </is>
-      </c>
-      <c r="B298" s="3" t="inlineStr"/>
-      <c r="C298" s="3" t="inlineStr"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="3" t="inlineStr">
-        <is>
-          <t>2610217C726Y1D</t>
-        </is>
-      </c>
-      <c r="B299" s="3" t="inlineStr"/>
-      <c r="C299" s="3" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="3" t="inlineStr">
-        <is>
-          <t>2610217C7P5S3N</t>
-        </is>
-      </c>
-      <c r="B300" s="3" t="inlineStr"/>
-      <c r="C300" s="3" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="3" t="inlineStr">
-        <is>
-          <t>2610217CFUH5DX</t>
-        </is>
-      </c>
-      <c r="B301" s="3" t="inlineStr"/>
-      <c r="C301" s="3" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="3" t="inlineStr">
-        <is>
-          <t>2610217CNGQPQY</t>
-        </is>
-      </c>
-      <c r="B302" s="3" t="inlineStr"/>
-      <c r="C302" s="3" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="3" t="inlineStr">
-        <is>
-          <t>2610217CSP7HYN</t>
-        </is>
-      </c>
-      <c r="B303" s="3" t="inlineStr"/>
-      <c r="C303" s="3" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="3" t="inlineStr">
-        <is>
-          <t>2610217E9PKXCW</t>
-        </is>
-      </c>
-      <c r="B304" s="3" t="inlineStr"/>
-      <c r="C304" s="3" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="3" t="inlineStr">
-        <is>
-          <t>2610217ETN7KWS</t>
-        </is>
-      </c>
-      <c r="B305" s="3" t="inlineStr"/>
-      <c r="C305" s="3" t="inlineStr"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="3" t="inlineStr">
-        <is>
-          <t>2610217F7GA8NP</t>
-        </is>
-      </c>
-      <c r="B306" s="3" t="inlineStr"/>
-      <c r="C306" s="3" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:C306"/>
+  <autoFilter ref="A1:C289"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2389,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -3335,8 +3110,66 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:28:27</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>261021882U112W</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: COA-002069 (วันที่: 2026-10-21 19:06, ราคาที่ต้องออกบิล: 0.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-21 19:06
+COA-002069 [ไม่จำหน่าย] MSI Folding Wagon รถเข็น ของแถมสำหรับจอ MSI ที่ร่วมรายการเท่านั้น
+ยิงขายขึ้น 3,000.00 บาท
+ลูกค้าซื้อราคา 0.00 บาท
+ขอวิธีปรับราคาครับ
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 0.00 บาท พอดีเป๊ะ:
+   • แนะนำ: 'DC2607230007' (ส่วนลด 3,000.00 บาท)
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:29:23</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>261021885HSPGR</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: MNL-002577 (วันที่: 2026-10-21 19:07, ราคาที่ต้องออกบิล: 9051.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-21 19:07
+MNL-002577 MSI Gaming Monitor MAG 321UPD E14 - 31.5"/IPS/4K 144Hz,FHD 288Hz/1ms/AMD FreeSync Premium/3Y*3 MNL-002577
+ยิงขายขึ้น 9,571.00 บาท
+ลูกค้าซื้อราคา 9,051.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D33"/>
+  <autoFilter ref="A1:D35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3347,7 +3180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C150"/>
+  <dimension ref="A1:C152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -5905,8 +5738,42 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30:15</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>2610218863WM9A</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:31:16</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>2610218A1EN9RQ</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C150"/>
+  <autoFilter ref="A1:C152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5917,7 +5784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I208"/>
+  <dimension ref="A1:I212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="4" min="1" max="1"/>
@@ -5978,7 +5845,7 @@
         </is>
       </c>
     </row>
-    <row r="2" s="4">
+    <row r="2" hidden="1" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:35:53</t>
@@ -6017,7 +5884,7 @@
         </is>
       </c>
     </row>
-    <row r="3" s="4">
+    <row r="3" hidden="1" s="4">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:36:48</t>
@@ -6056,7 +5923,7 @@
         </is>
       </c>
     </row>
-    <row r="4" s="4">
+    <row r="4" hidden="1" s="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:37:31</t>
@@ -6095,7 +5962,7 @@
         </is>
       </c>
     </row>
-    <row r="5" s="4">
+    <row r="5" hidden="1" s="4">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:37:54</t>
@@ -6134,7 +6001,7 @@
         </is>
       </c>
     </row>
-    <row r="6" s="4">
+    <row r="6" hidden="1" s="4">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:38:19</t>
@@ -6173,7 +6040,7 @@
         </is>
       </c>
     </row>
-    <row r="7" s="4">
+    <row r="7" hidden="1" s="4">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:38:19</t>
@@ -6212,7 +6079,7 @@
         </is>
       </c>
     </row>
-    <row r="8" s="4">
+    <row r="8" hidden="1" s="4">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:38:19</t>
@@ -6251,7 +6118,7 @@
         </is>
       </c>
     </row>
-    <row r="9" s="4">
+    <row r="9" hidden="1" s="4">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:38:19</t>
@@ -6290,7 +6157,7 @@
         </is>
       </c>
     </row>
-    <row r="10" s="4">
+    <row r="10" hidden="1" s="4">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:38:44</t>
@@ -6329,7 +6196,7 @@
         </is>
       </c>
     </row>
-    <row r="11" s="4">
+    <row r="11" hidden="1" s="4">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:38:44</t>
@@ -6368,7 +6235,7 @@
         </is>
       </c>
     </row>
-    <row r="12" s="4">
+    <row r="12" hidden="1" s="4">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:39:07</t>
@@ -6407,7 +6274,7 @@
         </is>
       </c>
     </row>
-    <row r="13" s="4">
+    <row r="13" hidden="1" s="4">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:39:52</t>
@@ -6446,7 +6313,7 @@
         </is>
       </c>
     </row>
-    <row r="14" s="4">
+    <row r="14" hidden="1" s="4">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:40:21</t>
@@ -6485,7 +6352,7 @@
         </is>
       </c>
     </row>
-    <row r="15" s="4">
+    <row r="15" hidden="1" s="4">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:41:03</t>
@@ -6524,7 +6391,7 @@
         </is>
       </c>
     </row>
-    <row r="16" s="4">
+    <row r="16" hidden="1" s="4">
       <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:41:28</t>
@@ -6563,7 +6430,7 @@
         </is>
       </c>
     </row>
-    <row r="17" s="4">
+    <row r="17" hidden="1" s="4">
       <c r="A17" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:42:27</t>
@@ -6603,7 +6470,7 @@
         </is>
       </c>
     </row>
-    <row r="18" s="4">
+    <row r="18" hidden="1" s="4">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:42:51</t>
@@ -6642,7 +6509,7 @@
         </is>
       </c>
     </row>
-    <row r="19" s="4">
+    <row r="19" hidden="1" s="4">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:43:33</t>
@@ -6681,7 +6548,7 @@
         </is>
       </c>
     </row>
-    <row r="20" s="4">
+    <row r="20" hidden="1" s="4">
       <c r="A20" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:44:12</t>
@@ -6720,7 +6587,7 @@
         </is>
       </c>
     </row>
-    <row r="21" s="4">
+    <row r="21" hidden="1" s="4">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:45:02</t>
@@ -6759,7 +6626,7 @@
         </is>
       </c>
     </row>
-    <row r="22" s="4">
+    <row r="22" hidden="1" s="4">
       <c r="A22" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:45:25</t>
@@ -6798,7 +6665,7 @@
         </is>
       </c>
     </row>
-    <row r="23" s="4">
+    <row r="23" hidden="1" s="4">
       <c r="A23" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:45:48</t>
@@ -6837,7 +6704,7 @@
         </is>
       </c>
     </row>
-    <row r="24" s="4">
+    <row r="24" hidden="1" s="4">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:46:32</t>
@@ -6876,7 +6743,7 @@
         </is>
       </c>
     </row>
-    <row r="25" s="4">
+    <row r="25" hidden="1" s="4">
       <c r="A25" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:46:32</t>
@@ -6915,7 +6782,7 @@
         </is>
       </c>
     </row>
-    <row r="26" s="4">
+    <row r="26" hidden="1" s="4">
       <c r="A26" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:46:32</t>
@@ -6954,7 +6821,7 @@
         </is>
       </c>
     </row>
-    <row r="27" s="4">
+    <row r="27" hidden="1" s="4">
       <c r="A27" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:46:32</t>
@@ -6993,7 +6860,7 @@
         </is>
       </c>
     </row>
-    <row r="28" s="4">
+    <row r="28" hidden="1" s="4">
       <c r="A28" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:46:32</t>
@@ -7032,7 +6899,7 @@
         </is>
       </c>
     </row>
-    <row r="29" s="4">
+    <row r="29" hidden="1" s="4">
       <c r="A29" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:47:06</t>
@@ -7072,7 +6939,7 @@
         </is>
       </c>
     </row>
-    <row r="30" s="4">
+    <row r="30" hidden="1" s="4">
       <c r="A30" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:47:46</t>
@@ -7111,7 +6978,7 @@
         </is>
       </c>
     </row>
-    <row r="31" s="4">
+    <row r="31" hidden="1" s="4">
       <c r="A31" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:48:23</t>
@@ -7150,7 +7017,7 @@
         </is>
       </c>
     </row>
-    <row r="32" s="4">
+    <row r="32" hidden="1" s="4">
       <c r="A32" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:49:04</t>
@@ -7189,7 +7056,7 @@
         </is>
       </c>
     </row>
-    <row r="33" s="4">
+    <row r="33" hidden="1" s="4">
       <c r="A33" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:49:31</t>
@@ -7228,7 +7095,7 @@
         </is>
       </c>
     </row>
-    <row r="34" s="4">
+    <row r="34" hidden="1" s="4">
       <c r="A34" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:49:56</t>
@@ -7267,7 +7134,7 @@
         </is>
       </c>
     </row>
-    <row r="35" s="4">
+    <row r="35" hidden="1" s="4">
       <c r="A35" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:50:31</t>
@@ -7313,7 +7180,7 @@
         </is>
       </c>
     </row>
-    <row r="36" s="4">
+    <row r="36" hidden="1" s="4">
       <c r="A36" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:51:00</t>
@@ -7352,7 +7219,7 @@
         </is>
       </c>
     </row>
-    <row r="37" s="4">
+    <row r="37" hidden="1" s="4">
       <c r="A37" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:51:42</t>
@@ -7392,7 +7259,7 @@
         </is>
       </c>
     </row>
-    <row r="38" s="4">
+    <row r="38" hidden="1" s="4">
       <c r="A38" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:52:05</t>
@@ -7431,7 +7298,7 @@
         </is>
       </c>
     </row>
-    <row r="39" s="4">
+    <row r="39" hidden="1" s="4">
       <c r="A39" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:52:05</t>
@@ -7470,7 +7337,7 @@
         </is>
       </c>
     </row>
-    <row r="40" s="4">
+    <row r="40" hidden="1" s="4">
       <c r="A40" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:52:45</t>
@@ -7509,7 +7376,7 @@
         </is>
       </c>
     </row>
-    <row r="41" s="4">
+    <row r="41" hidden="1" s="4">
       <c r="A41" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:53:40</t>
@@ -7548,7 +7415,7 @@
         </is>
       </c>
     </row>
-    <row r="42" s="4">
+    <row r="42" hidden="1" s="4">
       <c r="A42" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:53:40</t>
@@ -7587,7 +7454,7 @@
         </is>
       </c>
     </row>
-    <row r="43" s="4">
+    <row r="43" hidden="1" s="4">
       <c r="A43" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:53:40</t>
@@ -7626,7 +7493,7 @@
         </is>
       </c>
     </row>
-    <row r="44" s="4">
+    <row r="44" hidden="1" s="4">
       <c r="A44" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:54:06</t>
@@ -7665,7 +7532,7 @@
         </is>
       </c>
     </row>
-    <row r="45" s="4">
+    <row r="45" hidden="1" s="4">
       <c r="A45" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:54:59</t>
@@ -7704,7 +7571,7 @@
         </is>
       </c>
     </row>
-    <row r="46" s="4">
+    <row r="46" hidden="1" s="4">
       <c r="A46" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:55:56</t>
@@ -7743,7 +7610,7 @@
         </is>
       </c>
     </row>
-    <row r="47" s="4">
+    <row r="47" hidden="1" s="4">
       <c r="A47" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:56:36</t>
@@ -7782,7 +7649,7 @@
         </is>
       </c>
     </row>
-    <row r="48" s="4">
+    <row r="48" hidden="1" s="4">
       <c r="A48" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:57:40</t>
@@ -7821,7 +7688,7 @@
         </is>
       </c>
     </row>
-    <row r="49" s="4">
+    <row r="49" hidden="1" s="4">
       <c r="A49" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:58:04</t>
@@ -7860,7 +7727,7 @@
         </is>
       </c>
     </row>
-    <row r="50" s="4">
+    <row r="50" hidden="1" s="4">
       <c r="A50" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:58:49</t>
@@ -7899,7 +7766,7 @@
         </is>
       </c>
     </row>
-    <row r="51" s="4">
+    <row r="51" hidden="1" s="4">
       <c r="A51" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 15:59:27</t>
@@ -7938,7 +7805,7 @@
         </is>
       </c>
     </row>
-    <row r="52" s="4">
+    <row r="52" hidden="1" s="4">
       <c r="A52" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:00:08</t>
@@ -7977,7 +7844,7 @@
         </is>
       </c>
     </row>
-    <row r="53" s="4">
+    <row r="53" hidden="1" s="4">
       <c r="A53" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:00:53</t>
@@ -8016,7 +7883,7 @@
         </is>
       </c>
     </row>
-    <row r="54" s="4">
+    <row r="54" hidden="1" s="4">
       <c r="A54" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:00:53</t>
@@ -8055,7 +7922,7 @@
         </is>
       </c>
     </row>
-    <row r="55" s="4">
+    <row r="55" hidden="1" s="4">
       <c r="A55" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:01:23</t>
@@ -8094,7 +7961,7 @@
         </is>
       </c>
     </row>
-    <row r="56" s="4">
+    <row r="56" hidden="1" s="4">
       <c r="A56" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:02:16</t>
@@ -8133,7 +8000,7 @@
         </is>
       </c>
     </row>
-    <row r="57" s="4">
+    <row r="57" hidden="1" s="4">
       <c r="A57" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:02:58</t>
@@ -8172,7 +8039,7 @@
         </is>
       </c>
     </row>
-    <row r="58" s="4">
+    <row r="58" hidden="1" s="4">
       <c r="A58" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:03:47</t>
@@ -8211,7 +8078,7 @@
         </is>
       </c>
     </row>
-    <row r="59" s="4">
+    <row r="59" hidden="1" s="4">
       <c r="A59" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:04:22</t>
@@ -8250,7 +8117,7 @@
         </is>
       </c>
     </row>
-    <row r="60" s="4">
+    <row r="60" hidden="1" s="4">
       <c r="A60" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:05:08</t>
@@ -8289,7 +8156,7 @@
         </is>
       </c>
     </row>
-    <row r="61" s="4">
+    <row r="61" hidden="1" s="4">
       <c r="A61" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:06:03</t>
@@ -8329,7 +8196,7 @@
         </is>
       </c>
     </row>
-    <row r="62" s="4">
+    <row r="62" hidden="1" s="4">
       <c r="A62" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:06:42</t>
@@ -8368,7 +8235,7 @@
         </is>
       </c>
     </row>
-    <row r="63" s="4">
+    <row r="63" hidden="1" s="4">
       <c r="A63" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:08:02</t>
@@ -8408,7 +8275,7 @@
         </is>
       </c>
     </row>
-    <row r="64" s="4">
+    <row r="64" hidden="1" s="4">
       <c r="A64" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:08:47</t>
@@ -8447,7 +8314,7 @@
         </is>
       </c>
     </row>
-    <row r="65" s="4">
+    <row r="65" hidden="1" s="4">
       <c r="A65" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:09:12</t>
@@ -8486,7 +8353,7 @@
         </is>
       </c>
     </row>
-    <row r="66" s="4">
+    <row r="66" hidden="1" s="4">
       <c r="A66" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:09:58</t>
@@ -8525,7 +8392,7 @@
         </is>
       </c>
     </row>
-    <row r="67" s="4">
+    <row r="67" hidden="1" s="4">
       <c r="A67" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:11:03</t>
@@ -8565,7 +8432,7 @@
         </is>
       </c>
     </row>
-    <row r="68" s="4">
+    <row r="68" hidden="1" s="4">
       <c r="A68" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:11:31</t>
@@ -8604,7 +8471,7 @@
         </is>
       </c>
     </row>
-    <row r="69" s="4">
+    <row r="69" hidden="1" s="4">
       <c r="A69" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:11:55</t>
@@ -8643,7 +8510,7 @@
         </is>
       </c>
     </row>
-    <row r="70" s="4">
+    <row r="70" hidden="1" s="4">
       <c r="A70" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:12:23</t>
@@ -8682,7 +8549,7 @@
         </is>
       </c>
     </row>
-    <row r="71" s="4">
+    <row r="71" hidden="1" s="4">
       <c r="A71" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:13:16</t>
@@ -8721,7 +8588,7 @@
         </is>
       </c>
     </row>
-    <row r="72" s="4">
+    <row r="72" hidden="1" s="4">
       <c r="A72" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:14:05</t>
@@ -8760,7 +8627,7 @@
         </is>
       </c>
     </row>
-    <row r="73" s="4">
+    <row r="73" hidden="1" s="4">
       <c r="A73" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:14:44</t>
@@ -8799,7 +8666,7 @@
         </is>
       </c>
     </row>
-    <row r="74" s="4">
+    <row r="74" hidden="1" s="4">
       <c r="A74" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:15:22</t>
@@ -8843,7 +8710,7 @@
         </is>
       </c>
     </row>
-    <row r="75" s="4">
+    <row r="75" hidden="1" s="4">
       <c r="A75" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:16:10</t>
@@ -8882,7 +8749,7 @@
         </is>
       </c>
     </row>
-    <row r="76" s="4">
+    <row r="76" hidden="1" s="4">
       <c r="A76" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:16:53</t>
@@ -8921,7 +8788,7 @@
         </is>
       </c>
     </row>
-    <row r="77" s="4">
+    <row r="77" hidden="1" s="4">
       <c r="A77" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:17:38</t>
@@ -8960,7 +8827,7 @@
         </is>
       </c>
     </row>
-    <row r="78" s="4">
+    <row r="78" hidden="1" s="4">
       <c r="A78" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:18:23</t>
@@ -8999,7 +8866,7 @@
         </is>
       </c>
     </row>
-    <row r="79" s="4">
+    <row r="79" hidden="1" s="4">
       <c r="A79" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:19:13</t>
@@ -9038,7 +8905,7 @@
         </is>
       </c>
     </row>
-    <row r="80" s="4">
+    <row r="80" hidden="1" s="4">
       <c r="A80" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:19:13</t>
@@ -9077,7 +8944,7 @@
         </is>
       </c>
     </row>
-    <row r="81" s="4">
+    <row r="81" hidden="1" s="4">
       <c r="A81" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:19:13</t>
@@ -9116,7 +8983,7 @@
         </is>
       </c>
     </row>
-    <row r="82" s="4">
+    <row r="82" hidden="1" s="4">
       <c r="A82" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:20:02</t>
@@ -9155,7 +9022,7 @@
         </is>
       </c>
     </row>
-    <row r="83" s="4">
+    <row r="83" hidden="1" s="4">
       <c r="A83" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:20:49</t>
@@ -9199,7 +9066,7 @@
         </is>
       </c>
     </row>
-    <row r="84" s="4">
+    <row r="84" hidden="1" s="4">
       <c r="A84" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:21:50</t>
@@ -9239,7 +9106,7 @@
         </is>
       </c>
     </row>
-    <row r="85" s="4">
+    <row r="85" hidden="1" s="4">
       <c r="A85" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:22:35</t>
@@ -9278,7 +9145,7 @@
         </is>
       </c>
     </row>
-    <row r="86" s="4">
+    <row r="86" hidden="1" s="4">
       <c r="A86" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:23:06</t>
@@ -9322,7 +9189,7 @@
         </is>
       </c>
     </row>
-    <row r="87" s="4">
+    <row r="87" hidden="1" s="4">
       <c r="A87" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:23:49</t>
@@ -9361,7 +9228,7 @@
         </is>
       </c>
     </row>
-    <row r="88" s="4">
+    <row r="88" hidden="1" s="4">
       <c r="A88" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:24:28</t>
@@ -9405,7 +9272,7 @@
         </is>
       </c>
     </row>
-    <row r="89" s="4">
+    <row r="89" hidden="1" s="4">
       <c r="A89" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:25:35</t>
@@ -9444,7 +9311,7 @@
         </is>
       </c>
     </row>
-    <row r="90" s="4">
+    <row r="90" hidden="1" s="4">
       <c r="A90" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:25:59</t>
@@ -9483,7 +9350,7 @@
         </is>
       </c>
     </row>
-    <row r="91" s="4">
+    <row r="91" hidden="1" s="4">
       <c r="A91" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:26:38</t>
@@ -9522,7 +9389,7 @@
         </is>
       </c>
     </row>
-    <row r="92" s="4">
+    <row r="92" hidden="1" s="4">
       <c r="A92" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:27:18</t>
@@ -9561,7 +9428,7 @@
         </is>
       </c>
     </row>
-    <row r="93" s="4">
+    <row r="93" hidden="1" s="4">
       <c r="A93" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:27:57</t>
@@ -9600,7 +9467,7 @@
         </is>
       </c>
     </row>
-    <row r="94" s="4">
+    <row r="94" hidden="1" s="4">
       <c r="A94" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:28:41</t>
@@ -9639,7 +9506,7 @@
         </is>
       </c>
     </row>
-    <row r="95" s="4">
+    <row r="95" hidden="1" s="4">
       <c r="A95" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:29:25</t>
@@ -9678,7 +9545,7 @@
         </is>
       </c>
     </row>
-    <row r="96" s="4">
+    <row r="96" hidden="1" s="4">
       <c r="A96" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:30:08</t>
@@ -9717,7 +9584,7 @@
         </is>
       </c>
     </row>
-    <row r="97" s="4">
+    <row r="97" hidden="1" s="4">
       <c r="A97" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:30:29</t>
@@ -9756,7 +9623,7 @@
         </is>
       </c>
     </row>
-    <row r="98" s="4">
+    <row r="98" hidden="1" s="4">
       <c r="A98" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:31:21</t>
@@ -9795,7 +9662,7 @@
         </is>
       </c>
     </row>
-    <row r="99" s="4">
+    <row r="99" hidden="1" s="4">
       <c r="A99" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:32:04</t>
@@ -9834,7 +9701,7 @@
         </is>
       </c>
     </row>
-    <row r="100" s="4">
+    <row r="100" hidden="1" s="4">
       <c r="A100" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:32:39</t>
@@ -9874,7 +9741,7 @@
         </is>
       </c>
     </row>
-    <row r="101" s="4">
+    <row r="101" hidden="1" s="4">
       <c r="A101" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:33:34</t>
@@ -9914,7 +9781,7 @@
         </is>
       </c>
     </row>
-    <row r="102" s="4">
+    <row r="102" hidden="1" s="4">
       <c r="A102" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:34:14</t>
@@ -9953,7 +9820,7 @@
         </is>
       </c>
     </row>
-    <row r="103" s="4">
+    <row r="103" hidden="1" s="4">
       <c r="A103" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:35:26</t>
@@ -9992,7 +9859,7 @@
         </is>
       </c>
     </row>
-    <row r="104" s="4">
+    <row r="104" hidden="1" s="4">
       <c r="A104" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:35:26</t>
@@ -10031,7 +9898,7 @@
         </is>
       </c>
     </row>
-    <row r="105" s="4">
+    <row r="105" hidden="1" s="4">
       <c r="A105" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:35:26</t>
@@ -10070,7 +9937,7 @@
         </is>
       </c>
     </row>
-    <row r="106" s="4">
+    <row r="106" hidden="1" s="4">
       <c r="A106" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:35:54</t>
@@ -10109,7 +9976,7 @@
         </is>
       </c>
     </row>
-    <row r="107" s="4">
+    <row r="107" hidden="1" s="4">
       <c r="A107" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:35:54</t>
@@ -10148,7 +10015,7 @@
         </is>
       </c>
     </row>
-    <row r="108" s="4">
+    <row r="108" hidden="1" s="4">
       <c r="A108" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:36:36</t>
@@ -10187,7 +10054,7 @@
         </is>
       </c>
     </row>
-    <row r="109" s="4">
+    <row r="109" hidden="1" s="4">
       <c r="A109" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:37:15</t>
@@ -10226,7 +10093,7 @@
         </is>
       </c>
     </row>
-    <row r="110" s="4">
+    <row r="110" hidden="1" s="4">
       <c r="A110" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:37:38</t>
@@ -10265,7 +10132,7 @@
         </is>
       </c>
     </row>
-    <row r="111" s="4">
+    <row r="111" hidden="1" s="4">
       <c r="A111" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:38:00</t>
@@ -10304,7 +10171,7 @@
         </is>
       </c>
     </row>
-    <row r="112" s="4">
+    <row r="112" hidden="1" s="4">
       <c r="A112" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:39:44</t>
@@ -10344,7 +10211,7 @@
         </is>
       </c>
     </row>
-    <row r="113" s="4">
+    <row r="113" hidden="1" s="4">
       <c r="A113" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:40:23</t>
@@ -10384,7 +10251,7 @@
         </is>
       </c>
     </row>
-    <row r="114" s="4">
+    <row r="114" hidden="1" s="4">
       <c r="A114" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:40:46</t>
@@ -10423,7 +10290,7 @@
         </is>
       </c>
     </row>
-    <row r="115" s="4">
+    <row r="115" hidden="1" s="4">
       <c r="A115" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:41:11</t>
@@ -10462,7 +10329,7 @@
         </is>
       </c>
     </row>
-    <row r="116" s="4">
+    <row r="116" hidden="1" s="4">
       <c r="A116" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:41:54</t>
@@ -10501,7 +10368,7 @@
         </is>
       </c>
     </row>
-    <row r="117" s="4">
+    <row r="117" hidden="1" s="4">
       <c r="A117" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:42:21</t>
@@ -10540,7 +10407,7 @@
         </is>
       </c>
     </row>
-    <row r="118" s="4">
+    <row r="118" hidden="1" s="4">
       <c r="A118" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:42:41</t>
@@ -10579,7 +10446,7 @@
         </is>
       </c>
     </row>
-    <row r="119" s="4">
+    <row r="119" hidden="1" s="4">
       <c r="A119" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:42:47</t>
@@ -10606,7 +10473,7 @@
       <c r="H119" s="3" t="inlineStr"/>
       <c r="I119" s="3" t="inlineStr"/>
     </row>
-    <row r="120" s="4">
+    <row r="120" hidden="1" s="4">
       <c r="A120" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:43:27</t>
@@ -10645,7 +10512,7 @@
         </is>
       </c>
     </row>
-    <row r="121" s="4">
+    <row r="121" hidden="1" s="4">
       <c r="A121" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:44:08</t>
@@ -10684,7 +10551,7 @@
         </is>
       </c>
     </row>
-    <row r="122" s="4">
+    <row r="122" hidden="1" s="4">
       <c r="A122" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:44:47</t>
@@ -10724,7 +10591,7 @@
         </is>
       </c>
     </row>
-    <row r="123" s="4">
+    <row r="123" hidden="1" s="4">
       <c r="A123" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:45:25</t>
@@ -10764,7 +10631,7 @@
         </is>
       </c>
     </row>
-    <row r="124" s="4">
+    <row r="124" hidden="1" s="4">
       <c r="A124" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:46:05</t>
@@ -10804,7 +10671,7 @@
         </is>
       </c>
     </row>
-    <row r="125" s="4">
+    <row r="125" hidden="1" s="4">
       <c r="A125" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:46:43</t>
@@ -10844,7 +10711,7 @@
         </is>
       </c>
     </row>
-    <row r="126" s="4">
+    <row r="126" hidden="1" s="4">
       <c r="A126" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:47:07</t>
@@ -10883,7 +10750,7 @@
         </is>
       </c>
     </row>
-    <row r="127" s="4">
+    <row r="127" hidden="1" s="4">
       <c r="A127" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:47:46</t>
@@ -10922,7 +10789,7 @@
         </is>
       </c>
     </row>
-    <row r="128" s="4">
+    <row r="128" hidden="1" s="4">
       <c r="A128" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:48:28</t>
@@ -10961,7 +10828,7 @@
         </is>
       </c>
     </row>
-    <row r="129" s="4">
+    <row r="129" hidden="1" s="4">
       <c r="A129" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:49:07</t>
@@ -11000,7 +10867,7 @@
         </is>
       </c>
     </row>
-    <row r="130" s="4">
+    <row r="130" hidden="1" s="4">
       <c r="A130" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:49:50</t>
@@ -11039,7 +10906,7 @@
         </is>
       </c>
     </row>
-    <row r="131" s="4">
+    <row r="131" hidden="1" s="4">
       <c r="A131" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:50:15</t>
@@ -11078,7 +10945,7 @@
         </is>
       </c>
     </row>
-    <row r="132" s="4">
+    <row r="132" hidden="1" s="4">
       <c r="A132" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:50:39</t>
@@ -11117,7 +10984,7 @@
         </is>
       </c>
     </row>
-    <row r="133" s="4">
+    <row r="133" hidden="1" s="4">
       <c r="A133" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:51:21</t>
@@ -11156,7 +11023,7 @@
         </is>
       </c>
     </row>
-    <row r="134" s="4">
+    <row r="134" hidden="1" s="4">
       <c r="A134" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:51:27</t>
@@ -11183,7 +11050,7 @@
       <c r="H134" s="3" t="inlineStr"/>
       <c r="I134" s="3" t="inlineStr"/>
     </row>
-    <row r="135" s="4">
+    <row r="135" hidden="1" s="4">
       <c r="A135" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:51:27</t>
@@ -11210,7 +11077,7 @@
       <c r="H135" s="3" t="inlineStr"/>
       <c r="I135" s="3" t="inlineStr"/>
     </row>
-    <row r="136" s="4">
+    <row r="136" hidden="1" s="4">
       <c r="A136" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:51:50</t>
@@ -11249,7 +11116,7 @@
         </is>
       </c>
     </row>
-    <row r="137" s="4">
+    <row r="137" hidden="1" s="4">
       <c r="A137" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:52:09</t>
@@ -11288,7 +11155,7 @@
         </is>
       </c>
     </row>
-    <row r="138" s="4">
+    <row r="138" hidden="1" s="4">
       <c r="A138" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:52:46</t>
@@ -11327,7 +11194,7 @@
         </is>
       </c>
     </row>
-    <row r="139" s="4">
+    <row r="139" hidden="1" s="4">
       <c r="A139" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:53:31</t>
@@ -11366,7 +11233,7 @@
         </is>
       </c>
     </row>
-    <row r="140" s="4">
+    <row r="140" hidden="1" s="4">
       <c r="A140" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:54:13</t>
@@ -11405,7 +11272,7 @@
         </is>
       </c>
     </row>
-    <row r="141" s="4">
+    <row r="141" hidden="1" s="4">
       <c r="A141" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:54:52</t>
@@ -11444,7 +11311,7 @@
         </is>
       </c>
     </row>
-    <row r="142" s="4">
+    <row r="142" hidden="1" s="4">
       <c r="A142" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:55:20</t>
@@ -11483,7 +11350,7 @@
         </is>
       </c>
     </row>
-    <row r="143" s="4">
+    <row r="143" hidden="1" s="4">
       <c r="A143" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:56:00</t>
@@ -11522,7 +11389,7 @@
         </is>
       </c>
     </row>
-    <row r="144" s="4">
+    <row r="144" hidden="1" s="4">
       <c r="A144" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:56:23</t>
@@ -11561,7 +11428,7 @@
         </is>
       </c>
     </row>
-    <row r="145" s="4">
+    <row r="145" hidden="1" s="4">
       <c r="A145" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:56:29</t>
@@ -11588,7 +11455,7 @@
       <c r="H145" s="3" t="inlineStr"/>
       <c r="I145" s="3" t="inlineStr"/>
     </row>
-    <row r="146" s="4">
+    <row r="146" hidden="1" s="4">
       <c r="A146" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:56:29</t>
@@ -11615,7 +11482,7 @@
       <c r="H146" s="3" t="inlineStr"/>
       <c r="I146" s="3" t="inlineStr"/>
     </row>
-    <row r="147" s="4">
+    <row r="147" hidden="1" s="4">
       <c r="A147" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:56:29</t>
@@ -11642,7 +11509,7 @@
       <c r="H147" s="3" t="inlineStr"/>
       <c r="I147" s="3" t="inlineStr"/>
     </row>
-    <row r="148" s="4">
+    <row r="148" hidden="1" s="4">
       <c r="A148" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:57:03</t>
@@ -11686,7 +11553,7 @@
         </is>
       </c>
     </row>
-    <row r="149" s="4">
+    <row r="149" hidden="1" s="4">
       <c r="A149" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:57:43</t>
@@ -11725,7 +11592,7 @@
         </is>
       </c>
     </row>
-    <row r="150" s="4">
+    <row r="150" hidden="1" s="4">
       <c r="A150" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:58:23</t>
@@ -11764,7 +11631,7 @@
         </is>
       </c>
     </row>
-    <row r="151" s="4">
+    <row r="151" hidden="1" s="4">
       <c r="A151" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:58:28</t>
@@ -11791,7 +11658,7 @@
       <c r="H151" s="3" t="inlineStr"/>
       <c r="I151" s="3" t="inlineStr"/>
     </row>
-    <row r="152" s="4">
+    <row r="152" hidden="1" s="4">
       <c r="A152" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:58:28</t>
@@ -11818,7 +11685,7 @@
       <c r="H152" s="3" t="inlineStr"/>
       <c r="I152" s="3" t="inlineStr"/>
     </row>
-    <row r="153" s="4">
+    <row r="153" hidden="1" s="4">
       <c r="A153" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:58:28</t>
@@ -11845,7 +11712,7 @@
       <c r="H153" s="3" t="inlineStr"/>
       <c r="I153" s="3" t="inlineStr"/>
     </row>
-    <row r="154" s="4">
+    <row r="154" hidden="1" s="4">
       <c r="A154" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:58:50</t>
@@ -11884,7 +11751,7 @@
         </is>
       </c>
     </row>
-    <row r="155" s="4">
+    <row r="155" hidden="1" s="4">
       <c r="A155" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:59:09</t>
@@ -11923,7 +11790,7 @@
         </is>
       </c>
     </row>
-    <row r="156" s="4">
+    <row r="156" hidden="1" s="4">
       <c r="A156" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 16:59:49</t>
@@ -11962,7 +11829,7 @@
         </is>
       </c>
     </row>
-    <row r="157" s="4">
+    <row r="157" hidden="1" s="4">
       <c r="A157" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:00:29</t>
@@ -12001,7 +11868,7 @@
         </is>
       </c>
     </row>
-    <row r="158" s="4">
+    <row r="158" hidden="1" s="4">
       <c r="A158" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:01:08</t>
@@ -12040,7 +11907,7 @@
         </is>
       </c>
     </row>
-    <row r="159" s="4">
+    <row r="159" hidden="1" s="4">
       <c r="A159" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:01:42</t>
@@ -12080,7 +11947,7 @@
         </is>
       </c>
     </row>
-    <row r="160" s="4">
+    <row r="160" hidden="1" s="4">
       <c r="A160" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:02:02</t>
@@ -12119,7 +11986,7 @@
         </is>
       </c>
     </row>
-    <row r="161" s="4">
+    <row r="161" hidden="1" s="4">
       <c r="A161" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:02:53</t>
@@ -12158,7 +12025,7 @@
         </is>
       </c>
     </row>
-    <row r="162" s="4">
+    <row r="162" hidden="1" s="4">
       <c r="A162" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:03:32</t>
@@ -12198,7 +12065,7 @@
         </is>
       </c>
     </row>
-    <row r="163" s="4">
+    <row r="163" hidden="1" s="4">
       <c r="A163" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:03:56</t>
@@ -12237,7 +12104,7 @@
         </is>
       </c>
     </row>
-    <row r="164" s="4">
+    <row r="164" hidden="1" s="4">
       <c r="A164" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:04:39</t>
@@ -12276,7 +12143,7 @@
         </is>
       </c>
     </row>
-    <row r="165" s="4">
+    <row r="165" hidden="1" s="4">
       <c r="A165" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:04:39</t>
@@ -12315,7 +12182,7 @@
         </is>
       </c>
     </row>
-    <row r="166" s="4">
+    <row r="166" hidden="1" s="4">
       <c r="A166" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:05:04</t>
@@ -12354,7 +12221,7 @@
         </is>
       </c>
     </row>
-    <row r="167" s="4">
+    <row r="167" hidden="1" s="4">
       <c r="A167" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:05:44</t>
@@ -12393,7 +12260,7 @@
         </is>
       </c>
     </row>
-    <row r="168" s="4">
+    <row r="168" hidden="1" s="4">
       <c r="A168" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:05:44</t>
@@ -12432,7 +12299,7 @@
         </is>
       </c>
     </row>
-    <row r="169" s="4">
+    <row r="169" hidden="1" s="4">
       <c r="A169" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:05:44</t>
@@ -12471,7 +12338,7 @@
         </is>
       </c>
     </row>
-    <row r="170" s="4">
+    <row r="170" hidden="1" s="4">
       <c r="A170" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:05:44</t>
@@ -12510,7 +12377,7 @@
         </is>
       </c>
     </row>
-    <row r="171" s="4">
+    <row r="171" hidden="1" s="4">
       <c r="A171" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:06:04</t>
@@ -12549,7 +12416,7 @@
         </is>
       </c>
     </row>
-    <row r="172" s="4">
+    <row r="172" hidden="1" s="4">
       <c r="A172" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:06:43</t>
@@ -12588,7 +12455,7 @@
         </is>
       </c>
     </row>
-    <row r="173" s="4">
+    <row r="173" hidden="1" s="4">
       <c r="A173" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:07:22</t>
@@ -12627,7 +12494,7 @@
         </is>
       </c>
     </row>
-    <row r="174" s="4">
+    <row r="174" hidden="1" s="4">
       <c r="A174" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:08:00</t>
@@ -12666,7 +12533,7 @@
         </is>
       </c>
     </row>
-    <row r="175" s="4">
+    <row r="175" hidden="1" s="4">
       <c r="A175" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:08:24</t>
@@ -12705,7 +12572,7 @@
         </is>
       </c>
     </row>
-    <row r="176" s="4">
+    <row r="176" hidden="1" s="4">
       <c r="A176" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:09:06</t>
@@ -12744,7 +12611,7 @@
         </is>
       </c>
     </row>
-    <row r="177" s="4">
+    <row r="177" hidden="1" s="4">
       <c r="A177" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:09:49</t>
@@ -12783,7 +12650,7 @@
         </is>
       </c>
     </row>
-    <row r="178" s="4">
+    <row r="178" hidden="1" s="4">
       <c r="A178" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:10:16</t>
@@ -12822,7 +12689,7 @@
         </is>
       </c>
     </row>
-    <row r="179" s="4">
+    <row r="179" hidden="1" s="4">
       <c r="A179" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:10:56</t>
@@ -12861,7 +12728,7 @@
         </is>
       </c>
     </row>
-    <row r="180" s="4">
+    <row r="180" hidden="1" s="4">
       <c r="A180" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:11:21</t>
@@ -12900,7 +12767,7 @@
         </is>
       </c>
     </row>
-    <row r="181" s="4">
+    <row r="181" hidden="1" s="4">
       <c r="A181" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:11:58</t>
@@ -12939,7 +12806,7 @@
         </is>
       </c>
     </row>
-    <row r="182" s="4">
+    <row r="182" hidden="1" s="4">
       <c r="A182" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:12:35</t>
@@ -12979,7 +12846,7 @@
         </is>
       </c>
     </row>
-    <row r="183" s="4">
+    <row r="183" hidden="1" s="4">
       <c r="A183" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:13:00</t>
@@ -13018,7 +12885,7 @@
         </is>
       </c>
     </row>
-    <row r="184" s="4">
+    <row r="184" hidden="1" s="4">
       <c r="A184" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:13:38</t>
@@ -13057,7 +12924,7 @@
         </is>
       </c>
     </row>
-    <row r="185" s="4">
+    <row r="185" hidden="1" s="4">
       <c r="A185" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:14:09</t>
@@ -13103,7 +12970,7 @@
         </is>
       </c>
     </row>
-    <row r="186" s="4">
+    <row r="186" hidden="1" s="4">
       <c r="A186" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:14:49</t>
@@ -13142,7 +13009,7 @@
         </is>
       </c>
     </row>
-    <row r="187" s="4">
+    <row r="187" hidden="1" s="4">
       <c r="A187" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:14:49</t>
@@ -13181,7 +13048,7 @@
         </is>
       </c>
     </row>
-    <row r="188" s="4">
+    <row r="188" hidden="1" s="4">
       <c r="A188" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:15:29</t>
@@ -13220,7 +13087,7 @@
         </is>
       </c>
     </row>
-    <row r="189" s="4">
+    <row r="189" hidden="1" s="4">
       <c r="A189" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:16:07</t>
@@ -13259,7 +13126,7 @@
         </is>
       </c>
     </row>
-    <row r="190" s="4">
+    <row r="190" hidden="1" s="4">
       <c r="A190" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:16:48</t>
@@ -13298,7 +13165,7 @@
         </is>
       </c>
     </row>
-    <row r="191" s="4">
+    <row r="191" hidden="1" s="4">
       <c r="A191" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:17:24</t>
@@ -13337,7 +13204,7 @@
         </is>
       </c>
     </row>
-    <row r="192" s="4">
+    <row r="192" hidden="1" s="4">
       <c r="A192" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:17:45</t>
@@ -13376,7 +13243,7 @@
         </is>
       </c>
     </row>
-    <row r="193" s="4">
+    <row r="193" hidden="1" s="4">
       <c r="A193" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:18:56</t>
@@ -13415,7 +13282,7 @@
         </is>
       </c>
     </row>
-    <row r="194" s="4">
+    <row r="194" hidden="1" s="4">
       <c r="A194" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:18:56</t>
@@ -13454,7 +13321,7 @@
         </is>
       </c>
     </row>
-    <row r="195" s="4">
+    <row r="195" hidden="1" s="4">
       <c r="A195" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:19:38</t>
@@ -13493,7 +13360,7 @@
         </is>
       </c>
     </row>
-    <row r="196" s="4">
+    <row r="196" hidden="1" s="4">
       <c r="A196" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:20:20</t>
@@ -13532,7 +13399,7 @@
         </is>
       </c>
     </row>
-    <row r="197" s="4">
+    <row r="197" hidden="1" s="4">
       <c r="A197" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:21:03</t>
@@ -13571,7 +13438,7 @@
         </is>
       </c>
     </row>
-    <row r="198" s="4">
+    <row r="198" hidden="1" s="4">
       <c r="A198" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:21:26</t>
@@ -13610,7 +13477,7 @@
         </is>
       </c>
     </row>
-    <row r="199" s="4">
+    <row r="199" hidden="1" s="4">
       <c r="A199" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:22:03</t>
@@ -13650,7 +13517,7 @@
         </is>
       </c>
     </row>
-    <row r="200" s="4">
+    <row r="200" hidden="1" s="4">
       <c r="A200" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:22:56</t>
@@ -13689,7 +13556,7 @@
         </is>
       </c>
     </row>
-    <row r="201" s="4">
+    <row r="201" hidden="1" s="4">
       <c r="A201" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:23:40</t>
@@ -13728,7 +13595,7 @@
         </is>
       </c>
     </row>
-    <row r="202" s="4">
+    <row r="202" hidden="1" s="4">
       <c r="A202" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:24:13</t>
@@ -13768,7 +13635,7 @@
         </is>
       </c>
     </row>
-    <row r="203" s="4">
+    <row r="203" hidden="1" s="4">
       <c r="A203" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:24:35</t>
@@ -13807,7 +13674,7 @@
         </is>
       </c>
     </row>
-    <row r="204" s="4">
+    <row r="204" hidden="1" s="4">
       <c r="A204" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:24:35</t>
@@ -13846,7 +13713,7 @@
         </is>
       </c>
     </row>
-    <row r="205" s="4">
+    <row r="205" hidden="1" s="4">
       <c r="A205" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:25:20</t>
@@ -13892,7 +13759,7 @@
         </is>
       </c>
     </row>
-    <row r="206" s="4">
+    <row r="206" hidden="1" s="4">
       <c r="A206" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:26:00</t>
@@ -13932,7 +13799,7 @@
         </is>
       </c>
     </row>
-    <row r="207" s="4">
+    <row r="207" hidden="1" s="4">
       <c r="A207" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:26:48</t>
@@ -13971,7 +13838,7 @@
         </is>
       </c>
     </row>
-    <row r="208" s="4">
+    <row r="208" hidden="1" s="4">
       <c r="A208" s="3" t="inlineStr">
         <is>
           <t>2026-10-21 17:26:48</t>
@@ -14010,8 +13877,174 @@
         </is>
       </c>
     </row>
+    <row r="209" s="4">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:28:26</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>TH260125064166C</t>
+        </is>
+      </c>
+      <c r="C209" s="3" t="inlineStr">
+        <is>
+          <t>261021882U112W</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr"/>
+      <c r="E209" s="3" t="inlineStr"/>
+      <c r="F209" s="3" t="inlineStr"/>
+      <c r="G209" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H209" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: COA-002069 (วันที่: 2026-10-21 19:06, ราคาที่ต้องออกบิล: 0.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-21 19:06
+COA-002069 [ไม่จำหน่าย] MSI Folding Wagon รถเข็น ของแถมสำหรับจอ MSI ที่ร่วมรายการเท่านั้น
+ยิงขายขึ้น 3,000.00 บาท
+ลูกค้าซื้อราคา 0.00 บาท
+ขอวิธีปรับราคาครับ
+💡 [ระบบคำนวณแนะนำ] พบคูปองบน SMCO ที่ลดแล้วได้ราคา 0.00 บาท พอดีเป๊ะ:
+   • แนะนำ: 'DC2607230007' (ส่วนลด 3,000.00 บาท)
+   • บันทึกใส่คอลัมน์ 'suggested_cp' ใน cp_data.xlsx เรียบร้อยแล้ว (เปิดตรวจสอบและคัดลอกได้)
+ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" s="4">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:29:23</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr">
+        <is>
+          <t>TH2668202761008</t>
+        </is>
+      </c>
+      <c r="C210" s="3" t="inlineStr">
+        <is>
+          <t>261021885HSPGR</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr"/>
+      <c r="E210" s="3" t="inlineStr"/>
+      <c r="F210" s="3" t="inlineStr"/>
+      <c r="G210" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H210" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="I210" s="3" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: MNL-002577 (วันที่: 2026-10-21 19:07, ราคาที่ต้องออกบิล: 9051.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-21 19:07
+MNL-002577 MSI Gaming Monitor MAG 321UPD E14 - 31.5"/IPS/4K 144Hz,FHD 288Hz/1ms/AMD FreeSync Premium/3Y*3 MNL-002577
+ยิงขายขึ้น 9,571.00 บาท
+ลูกค้าซื้อราคา 9,051.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" s="4">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:30:15</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr">
+        <is>
+          <t>TH2615658578600</t>
+        </is>
+      </c>
+      <c r="C211" s="3" t="inlineStr">
+        <is>
+          <t>2610218863WM9A</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E211" s="3" t="inlineStr">
+        <is>
+          <t>2538.0</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="inlineStr">
+        <is>
+          <t>SU564M928</t>
+        </is>
+      </c>
+      <c r="G211" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
+        </is>
+      </c>
+      <c r="H211" s="3" t="inlineStr"/>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>MNL-002276: POS=2,538.00/เป้า=2,538.00 [ตรง ✅] | Total: POS=2,538.00/เป้า=2,538.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" s="4">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 14:31:16</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>TH268721603901A</t>
+        </is>
+      </c>
+      <c r="C212" s="3" t="inlineStr">
+        <is>
+          <t>2610218A1EN9RQ</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E212" s="3" t="inlineStr">
+        <is>
+          <t>2781.0</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="inlineStr"/>
+      <c r="G212" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H212" s="3" t="inlineStr"/>
+      <c r="I212" s="3" t="inlineStr">
+        <is>
+          <t>MNL-002412: POS=2,781.00/เป้า=2,781.00 [ตรง ✅] | Total: POS=2,781.00/เป้า=2,781.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I208"/>
+  <autoFilter ref="A1:I212"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/auto_page/autopageMKII/tables/Accel_mode_test.xlsx
+++ b/projects/auto_page/autopageMKII/tables/Accel_mode_test.xlsx
@@ -10,11 +10,13 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Failed_Orders" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Completed_Orders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Processed_Logs" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$C$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$D$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed_Orders'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$C$289</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Failed_Orders'!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Completed_Orders'!$A$1:$C$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Processed_Logs'!$A$1:$I$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -317,10 +319,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="4" min="1" max="1"/>
+    <col width="24" customWidth="1" style="4" min="1" max="1"/>
     <col width="12" customWidth="1" style="4" min="2" max="2"/>
     <col width="13" customWidth="1" style="4" min="3" max="3"/>
   </cols>
@@ -473,7 +475,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2610193CYMWY01</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
           <t>SU564TRMT</t>
@@ -512,7 +518,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>2610193FE3XPE3</t>
+        </is>
+      </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>SU564TN16</t>
@@ -525,7 +535,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>2610193G6VDH9D</t>
+        </is>
+      </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>SU564TRKN</t>
@@ -538,7 +552,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>2610193JY3BURK</t>
+        </is>
+      </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>SU564TNOH</t>
@@ -551,7 +569,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>2610193JY5795H</t>
+        </is>
+      </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>SU564TN1C</t>
@@ -564,7 +586,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>2610193K1NBH10</t>
+        </is>
+      </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
           <t>SU564TR44</t>
@@ -577,7 +603,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>2610193K24K1A0</t>
+        </is>
+      </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
           <t>SU564TR42</t>
@@ -590,7 +620,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>2610204NJEXWVM</t>
+        </is>
+      </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>SU564TN11</t>
@@ -602,8 +636,2312 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>2610204Q9XQQDT</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>2610204R3AB1YJ</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>2610204RMJFKJ3</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>2610204S1XPT9X</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>2610204S467PG8</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>2610204TCQ8DEM</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr"/>
+      <c r="B28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>2610204V9B1612</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>2610204VNWFVDF</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr"/>
+      <c r="B31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr"/>
+      <c r="B32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr"/>
+      <c r="B33" s="3" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>2610204W1AR6QT</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>2610204W79D5A5</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>2610204WBX6SEV</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>2610204YMGDYW7</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>2610204YXFW9G4</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>2610205049U8UK</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>261020504KD2VJ</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>26102050Q0R2YU</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>26102050XSN1DN</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr"/>
+      <c r="C42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>26102051T71EH0</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>261020522MYNH3</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>261020536F8WQD</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>26102053NA58M2</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr"/>
+      <c r="C46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>26102053TCB323</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>26102054CBDP7T</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>261020563T7108</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>26102056EU04FR</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr"/>
+      <c r="C50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr"/>
+      <c r="B51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>26102056PPTP5A</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>26102056PXEY8C</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>26102057970NC5</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>26102057SU5QRV</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>26102058U5CE1W</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>26102058WA1FFQ</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr"/>
+      <c r="B58" s="3" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>26102058WPDSWT</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>261020594SCCND</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>26102059NP3Q8A</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>26102059X6V0ST</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr"/>
+      <c r="C62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>2610205AQR7C5H</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr"/>
+      <c r="C63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>2610205BT2SXPW</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr"/>
+      <c r="C64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>2610205BWKBYNY</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr"/>
+      <c r="C65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>2610205C5KVGMR</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr"/>
+      <c r="B67" s="3" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>2610205C9TBFGF</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>2610205CASUW6N</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>2610205CASVS3U</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr"/>
+      <c r="C70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>2610205CASVS3V</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr"/>
+      <c r="B73" s="3" t="inlineStr"/>
+      <c r="C73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr"/>
+      <c r="B74" s="3" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr"/>
+      <c r="C75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr"/>
+      <c r="B76" s="3" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr"/>
+      <c r="B77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr"/>
+      <c r="B78" s="3" t="inlineStr"/>
+      <c r="C78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr"/>
+      <c r="B79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>2610205CDYVPEK</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>2610205CT8S089</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>2610205D58Q0TW</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>2610205DHCUBGF</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>2610205FNF148X</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr"/>
+      <c r="C84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>2610205FQKPQXJ</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>2610205G2A487N</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>2610205G9TDVEK</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr"/>
+      <c r="C87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>2610205GG0RJP3</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr"/>
+      <c r="C88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>2610205GTHDX0T</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr"/>
+      <c r="C89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>2610205JC2CXHC</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr"/>
+      <c r="C90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>2610205K0V2QCE</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr"/>
+      <c r="C91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>2610205K1KX372</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr"/>
+      <c r="C92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>2610205KU39SPS</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr"/>
+      <c r="C93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr"/>
+      <c r="C94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr"/>
+      <c r="B95" s="3" t="inlineStr"/>
+      <c r="C95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr"/>
+      <c r="C96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>2610205KXHY6J1</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr"/>
+      <c r="C97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>2610205MG0TMXX</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr"/>
+      <c r="C98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>2610205MSWCKV5</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr"/>
+      <c r="C99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>2610205P8RJJAR</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr"/>
+      <c r="C100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>2610205PB5T1B5</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr"/>
+      <c r="C101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>2610205QF228C5</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr"/>
+      <c r="C102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>2610205REK3DPP</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr"/>
+      <c r="C103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>2610205RGG3S2U</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr"/>
+      <c r="C104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>2610205RH6YHMS</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr"/>
+      <c r="C105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>2610205S3DPYRR</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr"/>
+      <c r="C106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>2610205TF1TFHF</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr"/>
+      <c r="C107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>2610205TS55GMF</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr"/>
+      <c r="C108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>2610205U0DUH9Q</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr"/>
+      <c r="C109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>2610205U47X2N9</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr"/>
+      <c r="C110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>2610205U7TABYF</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr"/>
+      <c r="C111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>2610205VC5TDB3</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr"/>
+      <c r="C112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>2610205VQ8JQ47</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr"/>
+      <c r="C113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>2610205VY0GVA1</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr"/>
+      <c r="C114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>2610205W9H7S74</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr"/>
+      <c r="C115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>2610205XC6AHM4</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr"/>
+      <c r="C116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>2610205YRQ3T98</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr"/>
+      <c r="C117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>26102061CEQGXC</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr"/>
+      <c r="C118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>26102063D18SXA</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr"/>
+      <c r="C119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>26102064M0QFCW</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr"/>
+      <c r="C120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr"/>
+      <c r="B121" s="3" t="inlineStr"/>
+      <c r="C121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>26102164T38JEK</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr"/>
+      <c r="C122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>26102167KCF00F</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr"/>
+      <c r="C123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>26102167WX2F3M</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr"/>
+      <c r="C124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>261021698D3D7C</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr"/>
+      <c r="C125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>261021699RWGC3</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr"/>
+      <c r="C126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>2610216AQB3V23</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr"/>
+      <c r="C127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>2610216AXF06QF</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr"/>
+      <c r="C128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>2610216AXSJ055</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr"/>
+      <c r="C129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>2610216BF435GM</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr"/>
+      <c r="C130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>2610216BV8Q9F0</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr"/>
+      <c r="C131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>2610216CUF74MR</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr"/>
+      <c r="C132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>2610216DBN2PX2</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>2610216J6FD2VU</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr"/>
+      <c r="C134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>2610216JQRGAP6</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr"/>
+      <c r="C135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>2610216SNPJAQA</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr"/>
+      <c r="C136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>2610216UJC80PE</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr"/>
+      <c r="C137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>2610216W9YSWT0</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr"/>
+      <c r="C138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>2610216YFS8D82</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr"/>
+      <c r="C139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>26102171E1FDBJ</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr"/>
+      <c r="C140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>26102172AJ41BU</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr"/>
+      <c r="C141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>26102173QYJSBU</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr"/>
+      <c r="C142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>26102174G7TQWP</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr"/>
+      <c r="C143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>26102174V4CWWB</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr"/>
+      <c r="C144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>26102175PQ0E4G</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr"/>
+      <c r="C145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>2610217620F70U</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr"/>
+      <c r="C146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>26102176SGXHMV</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr"/>
+      <c r="C147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>26102177CBNKNX</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr"/>
+      <c r="C148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>26102177UH3KJG</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr"/>
+      <c r="C149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>26102178RKWC4W</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr"/>
+      <c r="C150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>261021790BUYXV</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr"/>
+      <c r="C151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr"/>
+      <c r="B152" s="3" t="inlineStr"/>
+      <c r="C152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>261021796URVP2</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr"/>
+      <c r="C153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>26102179Q69ND5</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr"/>
+      <c r="C154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>2610217A4NBTHV</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr"/>
+      <c r="C155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>2610217BJ7JR54</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr"/>
+      <c r="C156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>2610217C726Y1D</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr"/>
+      <c r="C157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>2610217C7P5S3N</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr"/>
+      <c r="C158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>2610217CFUH5DX</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr"/>
+      <c r="C159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>2610217CHRJKME</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr"/>
+      <c r="C160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr"/>
+      <c r="B161" s="3" t="inlineStr"/>
+      <c r="C161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>2610217CNGQPQY</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr"/>
+      <c r="C162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>2610217CSP7HYN</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr"/>
+      <c r="C163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>2610217E9PKXCW</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr"/>
+      <c r="C164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>2610217EC1YCW1</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr"/>
+      <c r="C165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>2610217ETN7KWS</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr"/>
+      <c r="C166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>2610217F7GA8NP</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr"/>
+      <c r="C167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>2610217FT4BUN0</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr"/>
+      <c r="C168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>2610217FY0RG32</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr"/>
+      <c r="C169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>2610217G6SNNXB</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr"/>
+      <c r="C170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr"/>
+      <c r="B171" s="3" t="inlineStr"/>
+      <c r="C171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr"/>
+      <c r="B172" s="3" t="inlineStr"/>
+      <c r="C172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>2610217GDRRUQ6</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr"/>
+      <c r="C173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>2610217GJQ2VMC</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr"/>
+      <c r="C174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>2610217GT9BK4H</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr"/>
+      <c r="C175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>2610217GWCGUQT</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr"/>
+      <c r="C176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>2610217GWUR154</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr"/>
+      <c r="C177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>2610217H8N1NAB</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="inlineStr"/>
+      <c r="C178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>2610217HDP6A4U</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr"/>
+      <c r="C179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>2610217HDS2XGU</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="inlineStr"/>
+      <c r="C180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>2610217HKPSE9C</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr"/>
+      <c r="C181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>2610217J7C7XUY</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="inlineStr"/>
+      <c r="C182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>2610217J8M8F51</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr"/>
+      <c r="C183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>2610217J8S1Q5N</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="inlineStr"/>
+      <c r="C184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>2610217JBGSQ6D</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr"/>
+      <c r="C185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>2610217JDX2YRT</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="inlineStr"/>
+      <c r="C186" s="3" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>2610217K3N96EP</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="inlineStr"/>
+      <c r="C187" s="3" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>2610217KNCQBJ1</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="inlineStr"/>
+      <c r="C188" s="3" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr"/>
+      <c r="B189" s="3" t="inlineStr"/>
+      <c r="C189" s="3" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>2610217KRMM5V6</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr"/>
+      <c r="C190" s="3" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>2610217M3EV0JV</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="inlineStr"/>
+      <c r="C191" s="3" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>2610217MUFGR0Q</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr"/>
+      <c r="C192" s="3" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>2610217N4HDX8E</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="inlineStr"/>
+      <c r="C193" s="3" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>2610217N5SGGEU</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr"/>
+      <c r="C194" s="3" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>2610217N8H8FG8</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="inlineStr"/>
+      <c r="C195" s="3" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>2610217NE4GS7E</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr"/>
+      <c r="C196" s="3" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>2610217P2SCA70</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="inlineStr"/>
+      <c r="C197" s="3" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>2610217PCUS1BD</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="inlineStr"/>
+      <c r="C198" s="3" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>2610217PDFSB2K</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="inlineStr"/>
+      <c r="C199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>2610217QQCMKJV</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="inlineStr"/>
+      <c r="C200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>2610217SP62KSB</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr"/>
+      <c r="C201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>2610217SURDB3T</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="inlineStr"/>
+      <c r="C202" s="3" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>2610217SUW5C68</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr"/>
+      <c r="C203" s="3" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr"/>
+      <c r="B204" s="3" t="inlineStr"/>
+      <c r="C204" s="3" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>2610217T80A3VD</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr"/>
+      <c r="C205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>2610217THMCGHT</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="inlineStr"/>
+      <c r="C206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>2610217TWB66UV</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr"/>
+      <c r="C207" s="3" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>2610217UH87R2U</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="inlineStr"/>
+      <c r="C208" s="3" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>2610217W8M54KC</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr"/>
+      <c r="C209" s="3" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>2610217WJV6U0M</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="inlineStr"/>
+      <c r="C210" s="3" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>2610217WP44988</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="inlineStr"/>
+      <c r="C211" s="3" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>2610217X3CGA2X</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr"/>
+      <c r="C212" s="3" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>2610217XF82CF9</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr"/>
+      <c r="C213" s="3" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>2610217XXUU2DG</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr"/>
+      <c r="C214" s="3" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>2610217YR2NRGY</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="inlineStr"/>
+      <c r="C215" s="3" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>26102180M50AC2</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr"/>
+      <c r="C216" s="3" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>26102181XNV3XJ</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="inlineStr"/>
+      <c r="C217" s="3" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>261021839TS518</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr"/>
+      <c r="C218" s="3" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>26102183VRE69F</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="inlineStr"/>
+      <c r="C219" s="3" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>26102184A8CCY4</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="inlineStr"/>
+      <c r="C220" s="3" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>26102184XVATC5</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="inlineStr"/>
+      <c r="C221" s="3" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>26102185QMUJJD</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="inlineStr"/>
+      <c r="C222" s="3" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>261021865DFDY2</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr"/>
+      <c r="C223" s="3" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>26102186THKY2X</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr"/>
+      <c r="C224" s="3" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>261021882U112W</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr"/>
+      <c r="C225" s="3" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>261021885HSPGR</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="inlineStr"/>
+      <c r="C226" s="3" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>2610218863WM9A</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr"/>
+      <c r="C227" s="3" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>2610218A1EN9RQ</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr"/>
+      <c r="C228" s="3" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>2610218A2WCX78</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr"/>
+      <c r="C229" s="3" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr"/>
+      <c r="B230" s="3" t="inlineStr"/>
+      <c r="C230" s="3" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>2610218AQHBP4W</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="inlineStr"/>
+      <c r="C231" s="3" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>2610218AVNB1FC</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr"/>
+      <c r="C232" s="3" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>2610218B0GCAQ7</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="inlineStr"/>
+      <c r="C233" s="3" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>2610218B5CQQXM</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr"/>
+      <c r="C234" s="3" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>2610218B7GGDFK</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr"/>
+      <c r="C235" s="3" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>2610218BA3FF4J</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr"/>
+      <c r="C236" s="3" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>2610218BCU6S4C</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="inlineStr"/>
+      <c r="C237" s="3" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>2610218DKJ9V5R</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr"/>
+      <c r="C238" s="3" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>2610218E7H6T2H</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="inlineStr"/>
+      <c r="C239" s="3" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>2610218ESUQDK6</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr"/>
+      <c r="C240" s="3" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>2610218EYY7KAX</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="inlineStr"/>
+      <c r="C241" s="3" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>2610218F8UENKE</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="inlineStr"/>
+      <c r="C242" s="3" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>2610218G11UDDF</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="inlineStr"/>
+      <c r="C243" s="3" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>2610218G4FEJWN</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="inlineStr"/>
+      <c r="C244" s="3" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>2610218G8BDVQW</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr"/>
+      <c r="C245" s="3" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>2610218GBQ6XRH</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="inlineStr"/>
+      <c r="C246" s="3" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>2610218GP5YVPD</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr"/>
+      <c r="C247" s="3" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>2610218GY18E99</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="inlineStr"/>
+      <c r="C248" s="3" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>2610218J886G5W</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr"/>
+      <c r="C249" s="3" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>2610218JCCPEF3</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="inlineStr"/>
+      <c r="C250" s="3" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr"/>
+      <c r="B251" s="3" t="inlineStr"/>
+      <c r="C251" s="3" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>2610218MXF2W3H</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="inlineStr"/>
+      <c r="C252" s="3" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>2610228RM3AEUH</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="inlineStr"/>
+      <c r="C253" s="3" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>2610228RQMQNX5</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="inlineStr"/>
+      <c r="C254" s="3" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>2610228S1BMCY3</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="inlineStr"/>
+      <c r="C255" s="3" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>2610228S6A0634</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr"/>
+      <c r="C256" s="3" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>2610228TCJF8TJ</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="inlineStr"/>
+      <c r="C257" s="3" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>2610228TJXKXDG</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr"/>
+      <c r="C258" s="3" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>2610228TM5QH3H</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="inlineStr"/>
+      <c r="C259" s="3" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>2610228TPF30GW</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr"/>
+      <c r="C260" s="3" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>2610228U3A4JWC</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="inlineStr"/>
+      <c r="C261" s="3" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>2610228U5V70DP</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr"/>
+      <c r="C262" s="3" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>2610228UVQMWDA</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="inlineStr"/>
+      <c r="C263" s="3" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>2610228WVXTXFH</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="inlineStr"/>
+      <c r="C264" s="3" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>2610228WY6BNJ0</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="inlineStr"/>
+      <c r="C265" s="3" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>2610228XKY1A2F</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="inlineStr"/>
+      <c r="C266" s="3" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>261022933MPUE1</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr"/>
+      <c r="C267" s="3" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>26102298JPKH12</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="inlineStr"/>
+      <c r="C268" s="3" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>261022991HH9F2</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr"/>
+      <c r="C269" s="3" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>2610229BYS1YCY</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="inlineStr"/>
+      <c r="C270" s="3" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>2610229DK1AT9G</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr"/>
+      <c r="C271" s="3" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>2610229DQ412YT</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="inlineStr"/>
+      <c r="C272" s="3" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>2610229EGS5FMY</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr"/>
+      <c r="C273" s="3" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>2610229GUVC4XF</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="inlineStr"/>
+      <c r="C274" s="3" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>2610229J3QE34G</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="inlineStr"/>
+      <c r="C275" s="3" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>2610229JNGS9N4</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="inlineStr"/>
+      <c r="C276" s="3" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>2610229M4PDMS6</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="inlineStr"/>
+      <c r="C277" s="3" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>2610229MG8F05S</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr"/>
+      <c r="C278" s="3" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>2610229MHFJ44T</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="inlineStr"/>
+      <c r="C279" s="3" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>2610229P3U8XPD</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr"/>
+      <c r="C280" s="3" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>2610229Q0RC40D</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="inlineStr"/>
+      <c r="C281" s="3" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>2610229Q17JXN0</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr"/>
+      <c r="C282" s="3" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>2610229QQVCTYY</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="inlineStr"/>
+      <c r="C283" s="3" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>2610229R9F3D3X</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr"/>
+      <c r="C284" s="3" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>2610229RQ6PKUG</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="inlineStr"/>
+      <c r="C285" s="3" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>2610229RTMBCB4</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="inlineStr"/>
+      <c r="C286" s="3" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>2610229SA847C1</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="inlineStr"/>
+      <c r="C287" s="3" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>2610229SG5VYRN</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="inlineStr"/>
+      <c r="C288" s="3" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>2610229SS8SW92</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr"/>
+      <c r="C289" s="3" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C21"/>
+  <autoFilter ref="A1:C289"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -614,10 +2952,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="4" min="1" max="1"/>
+    <col width="22" customWidth="1" style="4" min="1" max="1"/>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
     <col width="24" customWidth="1" style="4" min="3" max="3"/>
     <col width="70" customWidth="1" style="4" min="4" max="4"/>
@@ -739,99 +3077,646 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:20:38</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2610193CACWCWH</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: MNL-002445 (วันที่: 2026-10-19 20:38, ราคาที่ต้องออกบิล: 2790.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-19 20:38
+MNL-002445 ACER Monitor EK251Q P6bmix - 24.5"/IPS/144Hz/1ms/AMD FreeSync/3Y*3 MNL-002445
+ยิงขายขึ้น 2,906.00 บาท
+ลูกค้าซื้อราคา 2,790.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D4"/>
+  <autoFilter ref="A1:D5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" style="3" min="1" max="1"/>
-    <col width="24" customWidth="1" style="3" min="2" max="2"/>
-    <col width="12" customWidth="1" style="3" min="3" max="4"/>
-    <col width="12" customWidth="1" style="4" min="4" max="4"/>
-    <col width="17" customWidth="1" style="3" min="5" max="5"/>
-    <col width="22" customWidth="1" style="3" min="6" max="6"/>
-    <col width="30" customWidth="1" style="3" min="7" max="7"/>
-    <col width="12" customWidth="1" style="3" min="8" max="8"/>
+    <col width="22" customWidth="1" style="4" min="1" max="1"/>
+    <col width="24" customWidth="1" style="4" min="2" max="2"/>
+    <col width="51" customWidth="1" style="4" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="4">
-      <c r="A1" s="5" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>orders</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24 17:52:57</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>260924TF1GJXH1</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:17:39</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>261018VUM91Y5D</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:17:44</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>261018VX4EDPFT</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:18:24</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>261018VY7W83FD</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:18:29</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>2610191F5RC4XV</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:18:34</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>26101925XQ8T15</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:19:11</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>2610192D546A58</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:19:34</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>2610192H08RY4Y</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:19:59</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>2610192Q0QJWHM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:20:04</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>26101935CSDC50</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" style="4" min="1" max="1"/>
+    <col width="20" customWidth="1" style="4" min="2" max="2"/>
+    <col width="24" customWidth="1" style="4" min="3" max="3"/>
+    <col width="15" customWidth="1" style="4" min="4" max="4"/>
+    <col width="15" customWidth="1" style="4" min="5" max="5"/>
+    <col width="20" customWidth="1" style="4" min="6" max="6"/>
+    <col width="51" customWidth="1" style="4" min="7" max="7"/>
+    <col width="18" customWidth="1" style="4" min="8" max="8"/>
+    <col width="70" customWidth="1" style="4" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>tracking</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>orders</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>bill_no</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>pricing_detail</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>sn</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>sn</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="4">
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>error_category</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" s="4">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>TH2633621075899</t>
+          <t>2026-10-22 16:17:39</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>260924TF1GJXH1</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24 17:52:57</t>
-        </is>
-      </c>
+          <t>TH264027490691M</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>261018VUM91Y5D</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr"/>
+      <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
           <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
         </is>
       </c>
+      <c r="H2" s="3" t="inlineStr"/>
+      <c r="I2" s="3" t="inlineStr"/>
+    </row>
+    <row r="3" s="4">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:17:44</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>TH013899BG144B</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>261018VX4EDPFT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ยกเลิกแล้ว)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4" s="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:18:24</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TH012899BG159C</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>261018VY7W83FD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2929.0</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>MNL-002194: POS=2,929.00/เป้า=2,929.00 [ตรง ✅] | Total: POS=2,929.00/เป้า=2,929.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" s="4">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:18:29</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TH260932550582Q</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2610191F5RC4XV</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="inlineStr"/>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6" s="4">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:18:34</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>TH2643306142916</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>26101925XQ8T15</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" s="4">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:19:11</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>TH262380818355C</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>2610192D546A58</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2781.0</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ปรับราคาและใส่คูปองสำเร็จ/All OK)</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>MNL-002412: POS=2,781.00/เป้า=2,781.00 [ตรง ✅] | Total: POS=2,781.00/เป้า=2,781.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" s="4">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:19:34</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>TH265207655771X</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>2610192H08RY4Y</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2906.0</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>MNL-002445: POS=2,906.00/เป้า=2,906.00 [ตรง ✅] | Total: POS=2,906.00/เป้า=2,906.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" s="4">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:19:59</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>TH264644676579T</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>2610192Q0QJWHM</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>TEST_MODE</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2972.0</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>TEST_SUCCESS (ราคาตรงตั้งแต่แรก/All OK)</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>MNL-002387: POS=2,972.00/เป้า=2,972.00 [ตรง ✅] | Total: POS=2,972.00/เป้า=2,972.00 [ตรง ✅]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" s="4">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:20:04</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>TH265254645187E</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>26101935CSDC50</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr"/>
+      <c r="F10" s="3" t="inlineStr"/>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>ข้าม (สถานะ: ส่งสินค้าแล้ว)</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" s="4">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-22 16:20:38</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>TH2622104429031</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>2610193CACWCWH</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_MISMATCH</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Order skipped, CP/DC not set for SKU: MNL-002445 (วันที่: 2026-10-19 20:38, ราคาที่ต้องออกบิล: 2790.0)
+SHOPEE เวลาสั่งซื้อ 2026-10-19 20:38
+MNL-002445 ACER Monitor EK251Q P6bmix - 24.5"/IPS/144Hz/1ms/AMD FreeSync/3Y*3 MNL-002445
+ยิงขายขึ้น 2,906.00 บาท
+ลูกค้าซื้อราคา 2,790.00 บาท
+ขอวิธีปรับราคาครับ (ด่านที่ติด: ตรวจสอบราคาและจำนวนสำเร็จ)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H2"/>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <autoFilter ref="A1:I11"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>